--- a/data/facility.xlsx
+++ b/data/facility.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codes\Python\PyCharm Projects\private-credit-performance\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C68510C-0D24-4D24-90F5-9C436E56FB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -52,8 +58,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,6 +73,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -102,27 +119,38 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -160,7 +188,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -194,6 +222,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -228,9 +257,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -403,11 +433,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,14 +468,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>60000000</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>90000000</v>
       </c>
       <c r="D2">
@@ -450,17 +488,17 @@
         <v>0.22</v>
       </c>
       <c r="G2">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>64000000</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>90000000</v>
       </c>
       <c r="D3">
@@ -473,40 +511,40 @@
         <v>0.2</v>
       </c>
       <c r="G3">
-        <v>0.046</v>
+        <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>68000000</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>90000000</v>
       </c>
       <c r="D4">
         <v>0.7</v>
       </c>
       <c r="E4">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="F4">
         <v>0.18</v>
       </c>
       <c r="G4">
-        <v>0.047</v>
+        <v>4.7E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>72000000</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>90000000</v>
       </c>
       <c r="D5">
@@ -519,7 +557,7 @@
         <v>0.15</v>
       </c>
       <c r="G5">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/facility.xlsx
+++ b/data/facility.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codes\Python\PyCharm Projects\private-credit-performance\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C68510C-0D24-4D24-90F5-9C436E56FB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>date</t>
   </si>
@@ -42,28 +36,15 @@
   <si>
     <t>cost_of_funds</t>
   </si>
-  <si>
-    <t>2024-09-30</t>
-  </si>
-  <si>
-    <t>2024-10-31</t>
-  </si>
-  <si>
-    <t>2024-11-30</t>
-  </si>
-  <si>
-    <t>2024-12-31</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,13 +54,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -119,38 +93,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -188,7 +152,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -222,7 +186,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -257,10 +220,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -433,19 +395,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,96 +422,280 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2">
-        <v>60000000</v>
-      </c>
-      <c r="C2" s="2">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2">
+        <v>45322</v>
+      </c>
+      <c r="B2">
+        <v>51879950</v>
+      </c>
+      <c r="C2">
         <v>90000000</v>
       </c>
       <c r="D2">
         <v>0.7</v>
       </c>
       <c r="E2">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="F2">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="G2">
-        <v>4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2">
-        <v>64000000</v>
-      </c>
-      <c r="C3" s="2">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2">
+        <v>45351</v>
+      </c>
+      <c r="B3">
+        <v>53962265</v>
+      </c>
+      <c r="C3">
         <v>90000000</v>
       </c>
       <c r="D3">
         <v>0.7</v>
       </c>
       <c r="E3">
+        <v>0.193</v>
+      </c>
+      <c r="F3">
+        <v>0.232</v>
+      </c>
+      <c r="G3">
+        <v>0.04527272727272727</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
+        <v>45382</v>
+      </c>
+      <c r="B4">
+        <v>56186235.5</v>
+      </c>
+      <c r="C4">
+        <v>90000000</v>
+      </c>
+      <c r="D4">
+        <v>0.7</v>
+      </c>
+      <c r="E4">
+        <v>0.186</v>
+      </c>
+      <c r="F4">
+        <v>0.224</v>
+      </c>
+      <c r="G4">
+        <v>0.04554545454545454</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2">
+        <v>45412</v>
+      </c>
+      <c r="B5">
+        <v>57789364.84999999</v>
+      </c>
+      <c r="C5">
+        <v>90000000</v>
+      </c>
+      <c r="D5">
+        <v>0.7</v>
+      </c>
+      <c r="E5">
+        <v>0.179</v>
+      </c>
+      <c r="F5">
+        <v>0.216</v>
+      </c>
+      <c r="G5">
+        <v>0.04581818181818181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
+        <v>45443</v>
+      </c>
+      <c r="B6">
+        <v>59317905.395</v>
+      </c>
+      <c r="C6">
+        <v>90000000</v>
+      </c>
+      <c r="D6">
+        <v>0.7</v>
+      </c>
+      <c r="E6">
+        <v>0.172</v>
+      </c>
+      <c r="F6">
+        <v>0.208</v>
+      </c>
+      <c r="G6">
+        <v>0.04609090909090909</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="B7">
+        <v>60277309.77649999</v>
+      </c>
+      <c r="C7">
+        <v>90000000</v>
+      </c>
+      <c r="D7">
+        <v>0.7</v>
+      </c>
+      <c r="E7">
+        <v>0.165</v>
+      </c>
+      <c r="F7">
+        <v>0.2</v>
+      </c>
+      <c r="G7">
+        <v>0.04636363636363636</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B8">
+        <v>60645718.84355</v>
+      </c>
+      <c r="C8">
+        <v>90000000</v>
+      </c>
+      <c r="D8">
+        <v>0.7</v>
+      </c>
+      <c r="E8">
+        <v>0.158</v>
+      </c>
+      <c r="F8">
+        <v>0.192</v>
+      </c>
+      <c r="G8">
+        <v>0.04663636363636364</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2">
+        <v>45535</v>
+      </c>
+      <c r="B9">
+        <v>60718241.19048499</v>
+      </c>
+      <c r="C9">
+        <v>90000000</v>
+      </c>
+      <c r="D9">
+        <v>0.7</v>
+      </c>
+      <c r="E9">
+        <v>0.151</v>
+      </c>
+      <c r="F9">
+        <v>0.184</v>
+      </c>
+      <c r="G9">
+        <v>0.04690909090909091</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2">
+        <v>45565</v>
+      </c>
+      <c r="B10">
+        <v>60353872.83333949</v>
+      </c>
+      <c r="C10">
+        <v>90000000</v>
+      </c>
+      <c r="D10">
+        <v>0.7</v>
+      </c>
+      <c r="E10">
+        <v>0.144</v>
+      </c>
+      <c r="F10">
+        <v>0.176</v>
+      </c>
+      <c r="G10">
+        <v>0.04718181818181818</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2">
+        <v>45596</v>
+      </c>
+      <c r="B11">
+        <v>59742468.98333764</v>
+      </c>
+      <c r="C11">
+        <v>90000000</v>
+      </c>
+      <c r="D11">
+        <v>0.7</v>
+      </c>
+      <c r="E11">
+        <v>0.137</v>
+      </c>
+      <c r="F11">
+        <v>0.168</v>
+      </c>
+      <c r="G11">
+        <v>0.04745454545454545</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2">
+        <v>45626</v>
+      </c>
+      <c r="B12">
+        <v>59138140.28833634</v>
+      </c>
+      <c r="C12">
+        <v>90000000</v>
+      </c>
+      <c r="D12">
+        <v>0.7</v>
+      </c>
+      <c r="E12">
+        <v>0.13</v>
+      </c>
+      <c r="F12">
         <v>0.16</v>
       </c>
-      <c r="F3">
-        <v>0.2</v>
-      </c>
-      <c r="G3">
-        <v>4.5999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2">
-        <v>68000000</v>
-      </c>
-      <c r="C4" s="2">
-        <v>90000000</v>
-      </c>
-      <c r="D4">
-        <v>0.7</v>
-      </c>
-      <c r="E4">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="F4">
-        <v>0.18</v>
-      </c>
-      <c r="G4">
-        <v>4.7E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2">
-        <v>72000000</v>
-      </c>
-      <c r="C5" s="2">
-        <v>90000000</v>
-      </c>
-      <c r="D5">
-        <v>0.7</v>
-      </c>
-      <c r="E5">
-        <v>0.12</v>
-      </c>
-      <c r="F5">
-        <v>0.15</v>
-      </c>
-      <c r="G5">
-        <v>4.8000000000000001E-2</v>
+      <c r="G12">
+        <v>0.04772727272727272</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B13">
+        <v>58448764.20183544</v>
+      </c>
+      <c r="C13">
+        <v>90000000</v>
+      </c>
+      <c r="D13">
+        <v>0.7</v>
+      </c>
+      <c r="E13">
+        <v>0.123</v>
+      </c>
+      <c r="F13">
+        <v>0.152</v>
+      </c>
+      <c r="G13">
+        <v>0.048</v>
       </c>
     </row>
   </sheetData>

--- a/data/facility.xlsx
+++ b/data/facility.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codes\Python\PyCharm Projects\private-credit-performance\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C44BF3-5264-48DB-8810-6D52E8FBEC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>date</t>
   </si>
@@ -35,16 +54,37 @@
   </si>
   <si>
     <t>cost_of_funds</t>
+  </si>
+  <si>
+    <t>eligible_collateral</t>
+  </si>
+  <si>
+    <t>borrowing_base_gross</t>
+  </si>
+  <si>
+    <t>reserve</t>
+  </si>
+  <si>
+    <t>borrowing_base_net</t>
+  </si>
+  <si>
+    <t>headroom</t>
+  </si>
+  <si>
+    <t>margin_call</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -54,6 +94,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -93,28 +140,43 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -152,7 +214,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -186,6 +248,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -220,9 +283,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -395,11 +459,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -421,281 +499,527 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>45322</v>
       </c>
-      <c r="B2">
-        <v>51879950</v>
-      </c>
-      <c r="C2">
-        <v>90000000</v>
-      </c>
-      <c r="D2">
-        <v>0.7</v>
-      </c>
-      <c r="E2">
-        <v>0.2</v>
-      </c>
-      <c r="F2">
-        <v>0.24</v>
-      </c>
-      <c r="G2">
-        <v>0.045</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="B2" s="3">
+        <v>57789497.741680667</v>
+      </c>
+      <c r="C2" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D2" s="5">
+        <f>I2/H2</f>
+        <v>0.69937783164757727</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="G2" s="4">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H2" s="3">
+        <v>119775600.8403361</v>
+      </c>
+      <c r="I2" s="3">
+        <v>83768400</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1197756.008403362</v>
+      </c>
+      <c r="K2" s="3">
+        <v>82570643.991596639</v>
+      </c>
+      <c r="L2" s="3">
+        <v>24781146.249915969</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45351</v>
       </c>
-      <c r="B3">
-        <v>53962265</v>
-      </c>
-      <c r="C3">
-        <v>90000000</v>
-      </c>
-      <c r="D3">
-        <v>0.7</v>
-      </c>
-      <c r="E3">
-        <v>0.193</v>
-      </c>
-      <c r="F3">
-        <v>0.232</v>
-      </c>
-      <c r="G3">
-        <v>0.04527272727272727</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="B3" s="3">
+        <v>64242539.730548702</v>
+      </c>
+      <c r="C3" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D3" s="5">
+        <f t="shared" ref="D3:D13" si="0">I3/H3</f>
+        <v>0.69828755079666061</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="G3" s="4">
+        <v>4.527272727272727E-2</v>
+      </c>
+      <c r="H3" s="3">
+        <v>125231465.068299</v>
+      </c>
+      <c r="I3" s="3">
+        <v>87447573.025220066</v>
+      </c>
+      <c r="J3" s="3">
+        <v>1252314.65068299</v>
+      </c>
+      <c r="K3" s="3">
+        <v>86195258.374537081</v>
+      </c>
+      <c r="L3" s="3">
+        <v>21952718.643988378</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45382</v>
       </c>
-      <c r="B4">
-        <v>56186235.5</v>
-      </c>
-      <c r="C4">
-        <v>90000000</v>
-      </c>
-      <c r="D4">
-        <v>0.7</v>
-      </c>
-      <c r="E4">
-        <v>0.186</v>
-      </c>
-      <c r="F4">
-        <v>0.224</v>
-      </c>
-      <c r="G4">
-        <v>0.04554545454545454</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="B4" s="3">
+        <v>69740425.636714324</v>
+      </c>
+      <c r="C4" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D4" s="5">
+        <f t="shared" si="0"/>
+        <v>0.69669911162872422</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="G4" s="4">
+        <v>4.5545454545454542E-2</v>
+      </c>
+      <c r="H4" s="3">
+        <v>130695849.8780524</v>
+      </c>
+      <c r="I4" s="3">
+        <v>91055682.50360021</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1306958.4987805239</v>
+      </c>
+      <c r="K4" s="3">
+        <v>89748724.004819691</v>
+      </c>
+      <c r="L4" s="3">
+        <v>20008298.368105371</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45412</v>
       </c>
-      <c r="B5">
-        <v>57789364.84999999</v>
-      </c>
-      <c r="C5">
-        <v>90000000</v>
-      </c>
-      <c r="D5">
-        <v>0.7</v>
-      </c>
-      <c r="E5">
-        <v>0.179</v>
-      </c>
-      <c r="F5">
-        <v>0.216</v>
-      </c>
-      <c r="G5">
-        <v>0.04581818181818181</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="B5" s="3">
+        <v>73643013.420384765</v>
+      </c>
+      <c r="C5" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D5" s="5">
+        <f t="shared" si="0"/>
+        <v>0.69662599984602436</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="G5" s="4">
+        <v>4.5818181818181813E-2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>130995070.54096361</v>
+      </c>
+      <c r="I5" s="3">
+        <v>91254571.990499258</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1309950.705409636</v>
+      </c>
+      <c r="K5" s="3">
+        <v>89944621.285089627</v>
+      </c>
+      <c r="L5" s="3">
+        <v>16301607.86470486</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45443</v>
       </c>
-      <c r="B6">
-        <v>59317905.395</v>
-      </c>
-      <c r="C6">
-        <v>90000000</v>
-      </c>
-      <c r="D6">
-        <v>0.7</v>
-      </c>
-      <c r="E6">
-        <v>0.172</v>
-      </c>
-      <c r="F6">
-        <v>0.208</v>
-      </c>
-      <c r="G6">
-        <v>0.04609090909090909</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="B6" s="3">
+        <v>76907067.008066714</v>
+      </c>
+      <c r="C6" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.69623350197831635</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.156</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.192</v>
+      </c>
+      <c r="G6" s="4">
+        <v>4.6090909090909092E-2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>133880136.3788593</v>
+      </c>
+      <c r="I6" s="3">
+        <v>93211836.196387798</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1338801.3637885931</v>
+      </c>
+      <c r="K6" s="3">
+        <v>91873034.832599208</v>
+      </c>
+      <c r="L6" s="3">
+        <v>14965967.82453249</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45473</v>
       </c>
-      <c r="B7">
-        <v>60277309.77649999</v>
-      </c>
-      <c r="C7">
-        <v>90000000</v>
-      </c>
-      <c r="D7">
-        <v>0.7</v>
-      </c>
-      <c r="E7">
-        <v>0.165</v>
-      </c>
-      <c r="F7">
-        <v>0.2</v>
-      </c>
-      <c r="G7">
-        <v>0.04636363636363636</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="B7" s="3">
+        <v>78711195.205320403</v>
+      </c>
+      <c r="C7" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.69630996171643189</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.185</v>
+      </c>
+      <c r="G7" s="4">
+        <v>4.6363636363636357E-2</v>
+      </c>
+      <c r="H7" s="3">
+        <v>131327445.9745463</v>
+      </c>
+      <c r="I7" s="3">
+        <v>91444608.878853112</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1313274.459745463</v>
+      </c>
+      <c r="K7" s="3">
+        <v>90131334.419107646</v>
+      </c>
+      <c r="L7" s="3">
+        <v>11420139.213787241</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45504</v>
       </c>
-      <c r="B8">
-        <v>60645718.84355</v>
-      </c>
-      <c r="C8">
-        <v>90000000</v>
-      </c>
-      <c r="D8">
-        <v>0.7</v>
-      </c>
-      <c r="E8">
-        <v>0.158</v>
-      </c>
-      <c r="F8">
-        <v>0.192</v>
-      </c>
-      <c r="G8">
-        <v>0.04663636363636364</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="B8" s="3">
+        <v>79556341.100608528</v>
+      </c>
+      <c r="C8" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.69615132692128001</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="G8" s="4">
+        <v>4.6636363636363642E-2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>129151932.3717443</v>
+      </c>
+      <c r="I8" s="3">
+        <v>89909289.095037222</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1291519.323717443</v>
+      </c>
+      <c r="K8" s="3">
+        <v>88617769.771319777</v>
+      </c>
+      <c r="L8" s="3">
+        <v>9061428.6707112491</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45535</v>
       </c>
-      <c r="B9">
-        <v>60718241.19048499</v>
-      </c>
-      <c r="C9">
-        <v>90000000</v>
-      </c>
-      <c r="D9">
-        <v>0.7</v>
-      </c>
-      <c r="E9">
-        <v>0.151</v>
-      </c>
-      <c r="F9">
-        <v>0.184</v>
-      </c>
-      <c r="G9">
-        <v>0.04690909090909091</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="B9" s="3">
+        <v>79894587.387064546</v>
+      </c>
+      <c r="C9" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.69604084214868667</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="G9" s="4">
+        <v>4.6909090909090907E-2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>127834683.36043081</v>
+      </c>
+      <c r="I9" s="3">
+        <v>88978160.662004963</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1278346.8336043081</v>
+      </c>
+      <c r="K9" s="3">
+        <v>87699813.828400657</v>
+      </c>
+      <c r="L9" s="3">
+        <v>7805226.4413361102</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45565</v>
       </c>
-      <c r="B10">
-        <v>60353872.83333949</v>
-      </c>
-      <c r="C10">
-        <v>90000000</v>
-      </c>
-      <c r="D10">
-        <v>0.7</v>
-      </c>
-      <c r="E10">
-        <v>0.144</v>
-      </c>
-      <c r="F10">
-        <v>0.176</v>
-      </c>
-      <c r="G10">
-        <v>0.04718181818181818</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="B10" s="3">
+        <v>77109462.143629014</v>
+      </c>
+      <c r="C10" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.70162968341492682</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="G10" s="4">
+        <v>4.7181818181818179E-2</v>
+      </c>
+      <c r="H10" s="3">
+        <v>110971103.7015647</v>
+      </c>
+      <c r="I10" s="3">
+        <v>77860620.358333856</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1109711.0370156469</v>
+      </c>
+      <c r="K10" s="3">
+        <v>76750909.321318209</v>
+      </c>
+      <c r="L10" s="3">
+        <v>-358552.82231080532</v>
+      </c>
+      <c r="M10" s="3">
+        <v>358552.82231080532</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45596</v>
       </c>
-      <c r="B11">
-        <v>59742468.98333764</v>
-      </c>
-      <c r="C11">
-        <v>90000000</v>
-      </c>
-      <c r="D11">
-        <v>0.7</v>
-      </c>
-      <c r="E11">
-        <v>0.137</v>
-      </c>
-      <c r="F11">
-        <v>0.168</v>
-      </c>
-      <c r="G11">
-        <v>0.04745454545454545</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="B11" s="3">
+        <v>74653260.817355648</v>
+      </c>
+      <c r="C11" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.70158581256488162</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.126</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.157</v>
+      </c>
+      <c r="G11" s="4">
+        <v>4.7454545454545451E-2</v>
+      </c>
+      <c r="H11" s="3">
+        <v>108324015.95879871</v>
+      </c>
+      <c r="I11" s="3">
+        <v>75998592.756744996</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1083240.159587987</v>
+      </c>
+      <c r="K11" s="3">
+        <v>74915352.597157016</v>
+      </c>
+      <c r="L11" s="3">
+        <v>262091.77980136871</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45626</v>
       </c>
-      <c r="B12">
-        <v>59138140.28833634</v>
-      </c>
-      <c r="C12">
-        <v>90000000</v>
-      </c>
-      <c r="D12">
-        <v>0.7</v>
-      </c>
-      <c r="E12">
-        <v>0.13</v>
-      </c>
-      <c r="F12">
-        <v>0.16</v>
-      </c>
-      <c r="G12">
-        <v>0.04772727272727272</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="B12" s="3">
+        <v>72669121.39623858</v>
+      </c>
+      <c r="C12" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.70152453996072384</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="G12" s="4">
+        <v>4.7727272727272722E-2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>106946223.155929</v>
+      </c>
+      <c r="I12" s="3">
+        <v>75025400</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1069462.2315592901</v>
+      </c>
+      <c r="K12" s="3">
+        <v>73955937.768440709</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1286816.3722021279</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45657</v>
       </c>
-      <c r="B13">
-        <v>58448764.20183544</v>
-      </c>
-      <c r="C13">
-        <v>90000000</v>
-      </c>
-      <c r="D13">
-        <v>0.7</v>
-      </c>
-      <c r="E13">
-        <v>0.123</v>
-      </c>
-      <c r="F13">
-        <v>0.152</v>
-      </c>
-      <c r="G13">
-        <v>0.048</v>
+      <c r="B13" s="3">
+        <v>70893376.138991654</v>
+      </c>
+      <c r="C13" s="3">
+        <v>90000000</v>
+      </c>
+      <c r="D13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.70159668985222923</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.114</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="G13" s="4">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="H13" s="3">
+        <v>104908419.70121381</v>
+      </c>
+      <c r="I13" s="3">
+        <v>73603400</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1049084.1970121381</v>
+      </c>
+      <c r="K13" s="3">
+        <v>72554315.802987859</v>
+      </c>
+      <c r="L13" s="3">
+        <v>1660939.663996205</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/facility.xlsx
+++ b/data/facility.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codes\Python\PyCharm Projects\private-credit-performance\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C44BF3-5264-48DB-8810-6D52E8FBEC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FB63DC-D78A-4B17-A0AF-D87032B3C11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -81,8 +81,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -145,15 +145,16 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -460,14 +461,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.28515625" bestFit="1" customWidth="1"/>
@@ -1022,6 +1023,9 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
